--- a/GBDS APRIL FILES 2026/PRICE LIST January.xlsx
+++ b/GBDS APRIL FILES 2026/PRICE LIST January.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98265E36-EA1E-487E-9FC1-6D85819CBB26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3795374-3636-4279-BC58-3853FDCCB462}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
